--- a/tiflow/develop/2.0.0-ballot.2/StructureDefinition-tiflow-order-task.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/StructureDefinition-tiflow-order-task.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
